--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_template.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_template.xlsx
@@ -380,6 +380,11 @@
           <t>Suicide</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Suicide</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -390,6 +395,11 @@
           <t>Blunt force Head Trauma</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CARDIAC ARREST</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -445,6 +455,12 @@
           <t>Medical</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Heart - Severe Athersclerotic &amp; Hypertensive CV disease
+ Date of birth is estimated. The decedent’s age at the time of death was 70. Gender was coded by the project as this information was not provided by DPSC.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -455,6 +471,11 @@
           <t>HEP C</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ESLD, Hep C, Cirrhosis</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -465,6 +486,11 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CEREBRAL VASCULAR</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -485,6 +511,11 @@
           <t>Natural</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -495,6 +526,11 @@
           <t>Natural</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -545,6 +581,11 @@
           <t>Blunt Force Head Injuries Homicide</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HOMICIDE-TRAUMATIC BRAIN INJURY</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -555,6 +596,11 @@
           <t>Natural</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -575,6 +621,11 @@
           <t>Natural Causes</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>COVID‐19</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -595,6 +646,11 @@
           <t>Natural</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -635,6 +691,11 @@
           <t>Metastatic Urothelial Carcinoma of the Renal Pelvis</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CANCER RENAL  W/METS</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -675,6 +736,11 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DIAABETES MELLITUS</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -735,6 +801,13 @@
           <t>Medical</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cancer.
+ Date of birth is estimated. The decedent's age at the time of death was 56.
+ Gender was coded by the project as this information was not provided by DPSC.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -760,6 +833,11 @@
           <t>Natural Causes</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Malignant Neoplasms</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -825,6 +903,11 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HEPATITIS C</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -880,6 +963,11 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CARDIAC ARREST</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -890,6 +978,11 @@
           <t>Natural Causes</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Diseases of the Heart</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -900,6 +993,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CA LIVER</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -910,6 +1008,11 @@
           <t>Natural</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -920,6 +1023,11 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>STAGE LIVER</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -930,6 +1038,11 @@
           <t>Natural</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -940,6 +1053,11 @@
           <t>RESPIRATORY FAILURE W/HYPOXIA, SEVERE SEPSIS</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Complications of Sepsis, Pneumonia</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -960,6 +1078,11 @@
           <t>Natural</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -980,6 +1103,11 @@
           <t>Hepatocellular Carcinoma</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CANCER-LIVER</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -990,6 +1118,11 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LUNG CANCER</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -1010,6 +1143,11 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ACUTE BRONCHOPNEUMONIA</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -1025,6 +1163,11 @@
       <c r="A60">
         <v>25024</v>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Metastatic Lung Cancer</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -1060,6 +1203,11 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CARDIAC ARREST</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -1070,6 +1218,11 @@
           <t>Natural</t>
         </is>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -1135,6 +1288,11 @@
       <c r="A70">
         <v>46023</v>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Liver Cancer</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -1205,6 +1363,11 @@
           <t>Natural</t>
         </is>
       </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -1230,6 +1393,11 @@
           <t>Natural</t>
         </is>
       </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -1245,6 +1413,11 @@
           <t>Natural</t>
         </is>
       </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Atherosclerotic CardiovascularDisease due to HTN</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -1255,6 +1428,11 @@
           <t>Illness</t>
         </is>
       </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>End stage liver disease HCV</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -1265,6 +1443,11 @@
           <t>Pending Investigation</t>
         </is>
       </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Pending Investigation</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -1275,16 +1458,31 @@
           <t>Natural</t>
         </is>
       </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
         <v>46242</v>
       </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Liver Cancer</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
         <v>34926</v>
       </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SCD</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -1330,6 +1528,11 @@
           <t>Natural</t>
         </is>
       </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -1410,6 +1613,11 @@
           <t>Natural Causes</t>
         </is>
       </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>COVID-19 Complications</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -1429,6 +1637,11 @@
     <row r="98">
       <c r="A98">
         <v>46090</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Hanging</t>
+        </is>
       </c>
     </row>
     <row r="99">

--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_template.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_template.xlsx
@@ -373,138 +373,102 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>31997</v>
+        <v>20811</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Suicide</t>
+          <t>Natural</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Suicide</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>27566</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Blunt force Head Trauma</t>
-        </is>
+        <v>24800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CARDIAC ARREST</t>
+          <t>CANCER OF THE ABDOMIN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>9676</v>
+        <v>19514</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Natural</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Shock Syndrome with Hypertension respiratory distress</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>14651</v>
+        <v>36363</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Metastatic Carcinoma of Unknown Origin</t>
+          <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>9245</v>
+        <v>347</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Oymchoma Cancer</t>
+          <t>Accidental Alcohol/drug intoxication (specify type)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>26035</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Heart - Severe Athersclerotic &amp; Hypertensive CV disease
- Date of birth is estimated. The decedent’s age at the time of death was 70. Gender was coded by the project as this information was not provided by DPSC.</t>
-        </is>
+        <v>30118</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>28270</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>HEP C</t>
-        </is>
+        <v>26908</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ESLD, Hep C, Cirrhosis</t>
+          <t>cardiac arrest</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>38376</v>
+        <v>9297</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CEREBRAL VASCULAR</t>
+          <t>Cardiac Arrest</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>21620</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NATURAL CAUSE</t>
-        </is>
+        <v>15591</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>19491</v>
+        <v>20964</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -519,7 +483,7 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>16801</v>
+        <v>43395</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -528,68 +492,83 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>All other illnesses</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>30761</v>
+        <v>4536</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Acute respiratory failure</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>15296</v>
+        <v>49054</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Complications of Metastatic Hepatocellular Carcinoma</t>
+          <t>Suicide</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>39792</v>
+        <v>14185</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Metastatic Testicular Cancer</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>43821</v>
+        <v>21342</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Natural</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>26891</v>
+        <v>33294</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blunt Force Head Injuries Homicide</t>
+          <t>NATURAL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HOMICIDE-TRAUMATIC BRAIN INJURY</t>
+          <t>CARDIAC ARREST</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>18004</v>
+        <v>19930</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -604,157 +583,142 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>40674</v>
+        <v>21899</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SUICIDE</t>
+          <t>NATURAL CAUSE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>31794</v>
+        <v>46752</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Natural Causes</t>
+          <t>Natural causes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>COVID‐19</t>
+          <t>Bronchopneumonia, End Stage Emphysema</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>45230</v>
+        <v>35453</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Natural</t>
+          <t>Natural Causes</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Under Review</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>18011</v>
+        <v>37765</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Natural</t>
+          <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>RESPIRATORY FAILURE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>10812</v>
+        <v>28078</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Ruptured Ilias Aneurysm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Periferal Vascular Disease</t>
+          <t>Aneurysm Ruptured</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>10965</v>
+        <v>41439</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>mutli-organ failure due to end-stage renal disease</t>
+          <t>SUICIDE</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>27078</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Metastatic Urothelial Carcinoma of the Renal Pelvis</t>
-        </is>
+        <v>34918</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CANCER RENAL  W/METS</t>
+          <t>IDIOPATHIC PULMONARY FIBROSIS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>5177</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Terminal Cancer</t>
-        </is>
+        <v>30057</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>6250</v>
+        <v>8331</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Lobar pneumonia</t>
+          <t>Accidental Alcohol/drug intoxication (specify type)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>37096</v>
+        <v>17615</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>Natural</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DIAABETES MELLITUS</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>39952</v>
+        <v>896</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Complications of Lung Cancer w/Sepsis &amp; Acute Respiratory Failure</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>13104</v>
+        <v>13181</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -763,165 +727,148 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>adult failure to thrive secondary to mult. comorbidities</t>
+          <t>LEUKEMIA</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>2498</v>
+        <v>43817</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Metastatic Bladder Cancer</t>
+          <t>Accident</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>41007</v>
+        <v>10472</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ACCIDENTAL</t>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Metastatic renal cell carcinoma</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>25938</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
+        <v>25008</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cancer.
- Date of birth is estimated. The decedent's age at the time of death was 56.
- Gender was coded by the project as this information was not provided by DPSC.</t>
+          <t>Cardiomyopathy</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>6219</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Acute bronchopneumonia complicating influenza A infection</t>
-        </is>
+        <v>47574</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>31761</v>
+        <v>23475</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Natural Causes</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Malignant Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>6435</v>
+        <v>27034</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Metastatic Adenocarcinoma to Brain</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Complications from Urinary Bladder Cancer</t>
+          <t>INTRACRANIAL BLEED DUE TO METS BRAIN CANCER</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>3115</v>
+        <v>27623</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Metastic CA Lung</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atherosclerotic and hypertensive Cardiovascular disease</t>
+          <t>cancer lung  w/ mets to brain</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>40702</v>
+        <v>49009</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>Natural Cause</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>8820</v>
+        <v>28344</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>CARDIO PULMONARY ARREST</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sarcomatoid Neoplasm of Liver w/Rupture &amp; Massive Hemoperitoneum</t>
+          <t>Cardiopumonary arrest</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>42872</v>
+        <v>6158</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HEPATITIS C</t>
+          <t>Metastatic sigmoid colon cancer</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>4955</v>
+        <v>17809</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Suicide (e.g. hanging, knife/cutting instrument, intentional drug overdose) – describe events</t>
+          <t>Natural</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>687</v>
+        <v>11286</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -930,93 +877,83 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Acute hepatic failure</t>
+          <t>AUTOIMMUNE HEPATITIS</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>40102</v>
+        <v>41258</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>NATURAL CAUSES/ILLNESS</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ACUTE CARDIAC ARRYTHMIA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>8545</v>
+        <v>38043</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Accidental Alcohol/drug intoxication (specify type)</t>
+          <t>NATURAL CAUSES/ILLNESS</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PRELIMINARY - CARDIORESPIRATORY FAILURE/DIABETES</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>42334</v>
+        <v>321</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CARDIAC ARREST</t>
+          <t>Other causes, specify causes</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>31540</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Natural Causes</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Diseases of the Heart</t>
-        </is>
+        <v>47847</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>35043</v>
+        <v>48642</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CA LIVER</t>
+          <t>Natural Cause</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>19089</v>
+        <v>46985</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Natural</t>
+          <t>Unavailable, investigation pending</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>Information received by the IDOC Investigations Unit indicated on January 23, 2024, at approximately 5:10 am, [redacted], informed Housing Unit 5 Correctional Officer [redacted] that [redacted], was unresponsive in his bed. [redacted] called a Code 3 (medical emergency) and, with the assistance of responding security staff, moved [redacted] to the floor and began CPR. Facility nursing staff responded, assessed [redacted], and requested emergency medical services (EMS) be called. [redacted] was transported to Jacksonville Memorial Hospital where [redacted] was pronounced deceased at 6:51 am.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>38250</v>
+        <v>38540</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1025,53 +962,58 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>STAGE LIVER</t>
+          <t>HYPERTENSIVE INTRACEREBRAL HEMORRHAGE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>17643</v>
+        <v>16431</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Natural</t>
+          <t>Accidental</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>28555</v>
+        <v>25849</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RESPIRATORY FAILURE W/HYPOXIA, SEVERE SEPSIS</t>
+          <t>Medical</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Complications of Sepsis, Pneumonia</t>
+          <t>end of stage liver disease</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>23558</v>
+        <v>13949</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Natural Causes</t>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Septicemia due to Metastic carcinoma of the breast</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>21312</v>
+        <v>17201</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1086,132 +1028,132 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>29465</v>
+        <v>42813</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Natural</t>
+          <t>SUICIDE</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>27508</v>
+        <v>36115</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hepatocellular Carcinoma</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>CANCER-LIVER</t>
+          <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>37746</v>
+        <v>12261</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LUNG CANCER</t>
+          <t>Acute Anterior Wall Myocardial Infarction (STEMI)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>40231</v>
+        <v>49179</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>Natural Cause</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>38359</v>
+        <v>29494</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>ACUTE BRONCHOPNEUMONIA</t>
+          <t>Undetermined</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>49142</v>
+        <v>10651</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Natural Cause</t>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Bilateral Pulmonary Thromboemboli.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>25024</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Metastatic Lung Cancer</t>
+        <v>39497</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>35654</v>
+        <v>46550</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>Natural causes</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On 03/30/2023 at 4:58 am, Registered [redacted] informed this reporting Major  [redacted] of the following incident.  While making rounds in the Stateville healthcare unit Registered Nurse [redacted] noticed Individual in Custody  [redacted] not breathing. Upon assessment of Individual in Custody [redacted] it was discovered that Individual in Custody [redacted] had no pulse, blood pressure, or respirations. No life saving measure was utilized, because Individual in Custody [redacted] had a DNR on file that was signed on 03/22/2023. Dr. [redacted] pronounced Individual in Custody [redacted] decease at 4:55 am. </t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>9607</v>
+        <v>21076</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Natural</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cardiopulmonary Arrest Secondary to Acute Hypoxic Respiratory Failure (Had a DNR)</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>38292</v>
+        <v>26156</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>Medical</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CARDIAC ARREST</t>
+          <t>Cardiopulmonary arrest as a result of cardiogenic shock</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>18966</v>
+        <v>20873</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -1226,7 +1168,7 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>3352</v>
+        <v>3076</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -1235,78 +1177,88 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Liver failure</t>
+          <t>Complications of Congestive heart failure, Atherosclerotic and Hypertensive cardiovascular disease</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>9914</v>
+        <v>4195</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Hypertensive &amp; Arteriosclerotic Cardiovascular Disease</t>
+          <t>Suicide (e.g. hanging, knife/cutting instrument, intentional drug overdose) – describe events</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>263</v>
+        <v>19998</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Natural</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pneumonia / Contributory Cause: Hypertensive Arteriosclerotic Cardiovascular Disease; Diabetes Melli</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>30778</v>
+        <v>44490</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>44172</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Natural</t>
+        <v>34372</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CAD</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>46023</v>
+        <v>4514</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+        </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Liver Cancer</t>
+          <t>Hepatocellular Cancer</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>9651</v>
+        <v>8943</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Acquired Immune Deficiency Syndrome (AIDS-related)</t>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Recurrect B Cell Lymphoma, w/Sepsis, C. Difficile Colitis &amp; Acute Renal Failure</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>9421</v>
+        <v>15288</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -1315,98 +1267,88 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RESPIRATORY FAILURE</t>
+          <t>Metastatic Adenocarcinoma</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>11446</v>
+        <v>44870</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>MULTI ORGAN FAILURE</t>
+          <t>Natural</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>30777</v>
+        <v>445</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Suicide (e.g. hanging, knife/cutting instrument, intentional drug overdose) – describe events</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>8065</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Complications of rectal carcinoma with metastases</t>
-        </is>
+        <v>48140</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>16000</v>
+        <v>3168</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Natural</t>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>Acute necrotizing bacterial bronchopneumonia with the underlying cause as squamous cell carcinoma...</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>15301</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
-        </is>
+        <v>35301</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Metastatic urothelial carcinoma</t>
+          <t>Under Review</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>20258</v>
+        <v>5267</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
+          <t>Homicide (all years except 2011 and 2012)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>47589</v>
+        <v>7816</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Respiratory Arrest</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>32199</v>
+        <v>21126</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -1415,88 +1357,98 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atherosclerotic CardiovascularDisease due to HTN</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>24366</v>
+        <v>27015</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Illness</t>
+          <t>Metastatic Liver Cancer</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>End stage liver disease HCV</t>
+          <t>Unsuccessful resuscitation</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>20129</v>
+        <v>12026</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pending Investigation</t>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pending Investigation</t>
+          <t>Complications of end stage liver disease due to hepatitis C</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>18275</v>
+        <v>7530</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Natural</t>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>Cirrhosis</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>46242</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Liver Cancer</t>
+        <v>22790</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>34926</v>
+        <v>3135</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+        </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SCD</t>
+          <t>Cardiac Arrest</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>4770</v>
+        <v>28661</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Accidental Alcohol/drug intoxication (specify type)</t>
+          <t>COVID-19, RESPIRATORY FAILURE</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Complications of COVID-19 Infection</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>745</v>
+        <v>5177</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -1505,23 +1457,28 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RECENT CEREBRAL INFARCT, PROBABLE SUBACUTE ENDOCARDITIS</t>
+          <t>Terminal Cancer</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>40174</v>
+        <v>16857</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>Natural</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>21500</v>
+        <v>18338</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -1536,17 +1493,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>22958</v>
+        <v>1284</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Suicide</t>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>MYOCARDIAL INFARCTION/HTN/BPH</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>14634</v>
+        <v>1248</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -1556,97 +1518,102 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>48780</v>
+        <v>40905</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Natural Cause</t>
+          <t>NATURAL CAUSES/ILLNESS</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>CARDIOPULMONARY ARREST</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>3904</v>
+        <v>35595</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Natural Causes</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Complications of acute myelomonocytic leukemia</t>
+          <t>Under Review</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>22066</v>
+        <v>5733</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NATURAL CAUSE</t>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Multiple myeloma</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>13090</v>
+        <v>44506</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Water intoxication due to psychogenic polydipsia</t>
+          <t>Natural</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>24499</v>
+        <v>18746</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Natural Causes</t>
+          <t>Suicide</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>COVID-19 Complications</t>
+          <t>Hanging,Strangulation</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>5286</v>
+        <v>35648</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>METASTIC PANCREATIC CANCER</t>
+          <t>NATURAL</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>46090</v>
+        <v>10025</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+        </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hanging</t>
+          <t>Renal failure</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>1403</v>
+        <v>2552</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -1655,22 +1622,37 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Natural- Acute Myocardial Infarction, Atherosclerotic Cardiovascular Disease</t>
+          <t>ACUTE CARDIORESPIRATORY FAILURE; METASTATIC PROSTATE CARCINOMA</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>48083</v>
+        <v>24276</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Illness</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Chronic destructive pulmonary disease</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>8053</v>
+        <v>36998</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Accidental Alcohol/drug intoxication (specify type)</t>
+          <t>NATURAL CAUSES/ILLNESS</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CONGESTIVE HEART</t>
         </is>
       </c>
     </row>

--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_template.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_template.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Suicide (e.g. hanging, knife/cutting instrument, intentional drug overdose) – describe events</t>
+          <t>Suicide</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Suicide (e.g. hanging, knife/cutting instrument, intentional drug overdose) – describe events</t>
+          <t>Suicide</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Suicide (e.g. hanging, knife/cutting instrument, intentional drug overdose) – describe events</t>
+          <t>Suicide</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Illness (exclude AIDS-related deaths), specify illness</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
